--- a/jaspr/web/cicada_ig/StructureDefinition-series-detail-ext.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-series-detail-ext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T22:18:14-04:00</t>
+    <t>2026-09-06T20:44:07-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/StructureDefinition-series-detail-ext.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-series-detail-ext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T20:44:07-04:00</t>
+    <t>2026-09-06T23:13:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/StructureDefinition-series-detail-ext.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-series-detail-ext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T23:13:14-04:00</t>
+    <t>2026-09-07T18:40:23-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/StructureDefinition-series-detail-ext.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-series-detail-ext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T18:40:23-04:00</t>
+    <t>2026-09-07T19:28:06-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/StructureDefinition-series-detail-ext.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-series-detail-ext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T19:28:06-04:00</t>
+    <t>2026-09-07T19:51:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
